--- a/luban-excels/bak/xlsx/Main - 副本.xlsx
+++ b/luban-excels/bak/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,9 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
+    <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
+    <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
   <si>
     <t>##var</t>
   </si>
@@ -46,7 +49,7 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>Rarity</t>
+    <t>ItemRarity</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -106,7 +109,7 @@
     <t>内部名称方便记忆</t>
   </si>
   <si>
-    <t>排序权重，数字越大约靠前</t>
+    <t>排序权重，数字越小约靠前</t>
   </si>
   <si>
     <t>盲盒权重</t>
@@ -128,7 +131,7 @@
 拿到字符串后需要自行转义
 该字段为列表，可以跨行填写多个
 要注意，也可以是tres文件
-由于小狗皮肤由多个文件组成，因此直接填写文件夹目录</t>
+由于小狗皮肤由多个文件组成，因此直接填写文件夹目录，卡面也是填文件夹</t>
   </si>
   <si>
     <t>在背包内显示的图标</t>
@@ -185,7 +188,7 @@
     <t>史诗</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Red\</t>
+    <t>v1\Shiba\Red\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Red.png</t>
@@ -197,7 +200,7 @@
     <t>黑柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Black\</t>
+    <t>v1\Shiba\Black\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Black.png</t>
@@ -209,7 +212,7 @@
     <t>白柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Cream\</t>
+    <t>v1\Shiba\Cream\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Cream.png</t>
@@ -221,7 +224,7 @@
     <t>胡麻柴</t>
   </si>
   <si>
-    <t>v1\Assets\Shiba\Sesame\</t>
+    <t>v1\Shiba\Sesame\</t>
   </si>
   <si>
     <t>v1\ItemIcon\Shiba_Sesame.png</t>
@@ -1151,7 +1154,7 @@
     <t>波尔多</t>
   </si>
   <si>
-    <t>沙特阿拉伯,阿联酋,马来西亚,印尼</t>
+    <t>沙特阿拉伯|阿联酋|马来西亚|印尼</t>
   </si>
   <si>
     <t>v1\Treat\Bordeaux.png</t>
@@ -1295,21 +1298,24 @@
     <t>CardFace</t>
   </si>
   <si>
-    <t>v1\Card\CardFace\</t>
+    <t>v1\Card\CardFace\Classic\</t>
+  </si>
+  <si>
+    <t>v1\ItemIcon\CardFace_Kibble.png</t>
+  </si>
+  <si>
+    <t>开发阶段先临时用经典卡面</t>
+  </si>
+  <si>
+    <t>Classic Card Face</t>
+  </si>
+  <si>
+    <t>经典卡面</t>
   </si>
   <si>
     <t>v1\ItemIcon\CardFace_Classic.png</t>
   </si>
   <si>
-    <t>开发阶段先临时用经典卡面</t>
-  </si>
-  <si>
-    <t>Classic Card Face</t>
-  </si>
-  <si>
-    <t>经典卡面</t>
-  </si>
-  <si>
     <t>小狗本体</t>
   </si>
   <si>
@@ -1322,6 +1328,12 @@
     <t>在全部国家隐藏</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
@@ -1337,6 +1349,12 @@
     <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
   </si>
   <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
@@ -1352,6 +1370,12 @@
     <t>United Arab Emirates赌博/宗教/酒精/色情</t>
   </si>
   <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
@@ -1367,6 +1391,12 @@
     <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
     <t>玩家手臂衣服</t>
   </si>
   <si>
@@ -1385,6 +1415,12 @@
     <t>Pakistan国家形象/政治</t>
   </si>
   <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -1403,6 +1439,12 @@
     <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
@@ -1415,6 +1457,12 @@
     <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
@@ -1427,6 +1475,12 @@
     <t>Russia赌博/LGBTQ/极端主义</t>
   </si>
   <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
     <t>玩家嗜好品</t>
   </si>
   <si>
@@ -1451,6 +1505,9 @@
     <t>North Korea国际制裁/政治</t>
   </si>
   <si>
+    <t>卡面</t>
+  </si>
+  <si>
     <t>SY</t>
   </si>
   <si>
@@ -1484,10 +1541,13 @@
     <t>Head</t>
   </si>
   <si>
-    <t>ClawLucky_Left_Back</t>
-  </si>
-  <si>
-    <t>ClawLucky_Right_Palms</t>
+    <t>Claw_Left_Back</t>
+  </si>
+  <si>
+    <t>Claw_Right_Palms</t>
+  </si>
+  <si>
+    <t>Tongue_Regular</t>
   </si>
   <si>
     <t>Ears_Happy</t>
@@ -1541,6 +1601,9 @@
     <t>狗右爪</t>
   </si>
   <si>
+    <t>舌头</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -1583,10 +1646,13 @@
     <t>Head_Chubby.png</t>
   </si>
   <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
   </si>
   <si>
     <t>Ears_Plane.png</t>
@@ -1697,6 +1763,9 @@
     <t>PayoutMultiplier</t>
   </si>
   <si>
+    <t>HandRank</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -1706,6 +1775,9 @@
     <t>SafeName_CN</t>
   </si>
   <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
     <t>赔率</t>
   </si>
   <si>
@@ -1718,6 +1790,9 @@
     <t>安全中文</t>
   </si>
   <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
     <t>Jacks or Better</t>
   </si>
   <si>
@@ -1727,6 +1802,9 @@
     <t>好犬优选</t>
   </si>
   <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
     <t>Two Pair</t>
   </si>
   <si>
@@ -1736,6 +1814,9 @@
     <t>双犬配对</t>
   </si>
   <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
     <t>Three of a Kind</t>
   </si>
   <si>
@@ -1763,6 +1844,9 @@
     <t>同色犬舍</t>
   </si>
   <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
     <t>Full House</t>
   </si>
   <si>
@@ -1772,6 +1856,9 @@
     <t>狗狗满堂</t>
   </si>
   <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
     <t>Four of a Kind</t>
   </si>
   <si>
@@ -1781,6 +1868,9 @@
     <t>四犬成团</t>
   </si>
   <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
     <t>Straight Flush</t>
   </si>
   <si>
@@ -1790,6 +1880,9 @@
     <t>纯种犬连击</t>
   </si>
   <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
     <t>Royal Flush</t>
   </si>
   <si>
@@ -1797,6 +1890,300 @@
   </si>
   <si>
     <t>皇家狗粮</t>
+  </si>
+  <si>
+    <t>FrameAssetPath</t>
+  </si>
+  <si>
+    <t>PlateAssetPath</t>
+  </si>
+  <si>
+    <t>边框</t>
+  </si>
+  <si>
+    <t>底板</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special2.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special2.png</t>
+  </si>
+  <si>
+    <t>TabName</t>
+  </si>
+  <si>
+    <t>*TabItemTypeList</t>
+  </si>
+  <si>
+    <t>list,EItemType</t>
+  </si>
+  <si>
+    <t>包含类型</t>
+  </si>
+  <si>
+    <t>在标签栏的顺序</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>DogReactionTrigger</t>
+  </si>
+  <si>
+    <t>AssetRef</t>
+  </si>
+  <si>
+    <t>EarAsset</t>
+  </si>
+  <si>
+    <t>EyeAsset</t>
+  </si>
+  <si>
+    <t>OverrideHeadwear</t>
+  </si>
+  <si>
+    <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>LeftPawAnimation</t>
+  </si>
+  <si>
+    <t>RightPawAnimation</t>
+  </si>
+  <si>
+    <t>TongueAnimation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>EDogReactionTrigger</t>
+  </si>
+  <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>戴上眼镜</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>手心，摆手</t>
+  </si>
+  <si>
+    <t>WaitingForBet</t>
+  </si>
+  <si>
+    <t>等待下注时</t>
+  </si>
+  <si>
+    <t>默认，该品种狗默认表情</t>
+  </si>
+  <si>
+    <t>Dealt</t>
+  </si>
+  <si>
+    <t>等待玩家选牌</t>
+  </si>
+  <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
+    <t>玩家选牌中等待询问时</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问</t>
+  </si>
+  <si>
+    <t>HintResult</t>
+  </si>
+  <si>
+    <t>展示询问结果</t>
+  </si>
+  <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+  </si>
+  <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
+    <t>询问机会用尽</t>
+  </si>
+  <si>
+    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
+  </si>
+  <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
+    <t>拒绝询问</t>
+  </si>
+  <si>
+    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
+  </si>
+  <si>
+    <t>严肃，面无表情</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>看到结算结果</t>
+  </si>
+  <si>
+    <t>根据牌型优劣作出相应表情</t>
+  </si>
+  <si>
+    <t>SawNothing</t>
+  </si>
+  <si>
+    <t>看到坏牌</t>
+  </si>
+  <si>
+    <t>SawJacksOrBetter</t>
+  </si>
+  <si>
+    <t>看到高对</t>
+  </si>
+  <si>
+    <t>SawTwoPair</t>
+  </si>
+  <si>
+    <t>看到两对</t>
+  </si>
+  <si>
+    <t>SawThreeOfAKind</t>
+  </si>
+  <si>
+    <t>看到三条</t>
+  </si>
+  <si>
+    <t>SawStraight</t>
+  </si>
+  <si>
+    <t>看到顺子</t>
+  </si>
+  <si>
+    <t>SawFlush</t>
+  </si>
+  <si>
+    <t>看到同花</t>
+  </si>
+  <si>
+    <t>SawFullHouse</t>
+  </si>
+  <si>
+    <t>看到葫芦</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
+    <t>SawFourOfAKind</t>
+  </si>
+  <si>
+    <t>看到四条</t>
+  </si>
+  <si>
+    <t>SawStraightFlush</t>
+  </si>
+  <si>
+    <t>看到同花顺</t>
+  </si>
+  <si>
+    <t>SawRoyalFlush</t>
+  </si>
+  <si>
+    <t>看到皇家同花顺</t>
   </si>
 </sst>
 </file>
@@ -2417,7 +2804,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2427,14 +2814,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2967,7 +3357,8 @@
     <col min="3" max="3" width="20.4166666666667" customWidth="1"/>
     <col min="4" max="4" width="20.0833333333333" customWidth="1"/>
     <col min="8" max="8" width="14.3333333333333" customWidth="1"/>
-    <col min="10" max="11" width="17.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="27.4166666666667" customWidth="1"/>
+    <col min="11" max="11" width="17.5833333333333" customWidth="1"/>
     <col min="12" max="12" width="9.91666666666667" customWidth="1"/>
     <col min="13" max="13" width="44" customWidth="1"/>
     <col min="14" max="14" width="55.9166666666667" customWidth="1"/>
@@ -3064,7 +3455,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="5" customFormat="1" ht="104.4" spans="1:16">
+    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -3073,28 +3464,28 @@
       <c r="D3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4586,13 +4977,13 @@
         <v>300</v>
       </c>
       <c r="H45">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M45" t="s">
         <v>205</v>
@@ -5076,13 +5467,13 @@
         <v>300</v>
       </c>
       <c r="H59">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>262</v>
@@ -6540,7 +6931,7 @@
         <v>419</v>
       </c>
       <c r="N98" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
@@ -6552,311 +6943,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M13"/>
+  <dimension ref="B2:P13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:16">
+      <c r="B2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>424</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13">
-      <c r="B3" s="4" t="s">
+      <c r="K2" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C3" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="4" t="s">
+      <c r="K3" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="H4" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="L4" s="4">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="4" t="s">
+      <c r="K4" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
+      <c r="B5" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>438</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="C5" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>440</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="L5" s="4">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="4" t="s">
+      <c r="K5" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
+      <c r="B6" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="D6" s="4">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="L6" s="4">
+      <c r="C6" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="4" t="s">
+      <c r="K6" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
+      <c r="B7" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="4">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="L7" s="4">
+      <c r="C7" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="4" t="s">
+      <c r="K7" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
+      <c r="B8" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>455</v>
-      </c>
-      <c r="D8" s="4">
-        <v>7</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="L8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="4" t="s">
+      <c r="K8" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
+      <c r="B9" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="D9" s="4">
-        <v>8</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="L9" s="4">
+      <c r="C9" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>475</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="M9" s="4" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="4" t="s">
+      <c r="K9" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="P9" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
+      <c r="B10" s="5" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="L10" s="4">
+      <c r="C10" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="4" t="s">
+      <c r="K10" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
+      <c r="B11" s="5" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="D11" s="4">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="L11" s="4">
+      <c r="C11" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="M11" s="4" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="J12" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="L12" s="4">
+      <c r="K11" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="B12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" t="s">
+        <v>488</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="J13" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="L13" s="4">
+      <c r="K12" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="H13" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>493</v>
+      </c>
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>476</v>
+      <c r="K13" s="5" t="s">
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -6868,28 +7283,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
     <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
-    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
+    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
+    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6898,52 +7313,55 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="I1" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="J1" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="K1" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="L1" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="M1" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="N1" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="O1" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="P1" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="Q1" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="R1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>509</v>
+      </c>
+      <c r="S1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -6996,8 +7414,11 @@
       <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:18">
+      <c r="S2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -7005,15 +7426,15 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -7021,108 +7442,114 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="F4" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="G4" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="I4" t="s">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="J4" t="s">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="K4" t="s">
-        <v>501</v>
+        <v>520</v>
       </c>
       <c r="L4" t="s">
-        <v>502</v>
+        <v>521</v>
       </c>
       <c r="M4" t="s">
-        <v>503</v>
+        <v>522</v>
       </c>
       <c r="N4" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="O4" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="P4" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="Q4" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="R4" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>527</v>
+      </c>
+      <c r="S4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="H5" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I5" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J5" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K5" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L5" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M5" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N5" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O5" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P5" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q5" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -7130,52 +7557,55 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>523</v>
+        <v>544</v>
       </c>
       <c r="E6" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F6" t="s">
-        <v>519</v>
+        <v>540</v>
       </c>
       <c r="G6" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="H6" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I6" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J6" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K6" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L6" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M6" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N6" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O6" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P6" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q6" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R6" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -7183,52 +7613,55 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>525</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F7" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="G7" t="s">
-        <v>526</v>
+        <v>547</v>
       </c>
       <c r="H7" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I7" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J7" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K7" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L7" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M7" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N7" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O7" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P7" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q7" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R7" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -7236,52 +7669,55 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>527</v>
+        <v>548</v>
       </c>
       <c r="E8" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="F8" t="s">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="G8" t="s">
-        <v>528</v>
+        <v>549</v>
       </c>
       <c r="H8" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="I8" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J8" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K8" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L8" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M8" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N8" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O8" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P8" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q8" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -7289,52 +7725,55 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="E9" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F9" t="s">
-        <v>520</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
       <c r="H9" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="I9" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J9" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K9" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L9" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M9" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N9" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O9" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P9" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q9" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S9" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -7342,52 +7781,55 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" t="s">
+        <v>532</v>
+      </c>
+      <c r="G10" t="s">
+        <v>533</v>
+      </c>
+      <c r="H10" t="s">
+        <v>553</v>
+      </c>
+      <c r="I10" t="s">
+        <v>535</v>
+      </c>
+      <c r="J10" t="s">
+        <v>536</v>
+      </c>
+      <c r="K10" t="s">
+        <v>537</v>
+      </c>
+      <c r="L10" t="s">
         <v>531</v>
       </c>
-      <c r="E10" t="s">
-        <v>517</v>
-      </c>
-      <c r="F10" t="s">
-        <v>512</v>
-      </c>
-      <c r="G10" t="s">
-        <v>513</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="M10" t="s">
+        <v>538</v>
+      </c>
+      <c r="N10" t="s">
+        <v>539</v>
+      </c>
+      <c r="O10" t="s">
         <v>532</v>
       </c>
-      <c r="I10" t="s">
-        <v>515</v>
-      </c>
-      <c r="J10" t="s">
-        <v>516</v>
-      </c>
-      <c r="K10" t="s">
-        <v>511</v>
-      </c>
-      <c r="L10" t="s">
-        <v>517</v>
-      </c>
-      <c r="M10" t="s">
-        <v>518</v>
-      </c>
-      <c r="N10" t="s">
-        <v>512</v>
-      </c>
-      <c r="O10" t="s">
-        <v>519</v>
-      </c>
       <c r="P10" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q10" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R10" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -7395,52 +7837,55 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>533</v>
+        <v>554</v>
       </c>
       <c r="E11" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F11" t="s">
-        <v>522</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="H11" t="s">
-        <v>530</v>
+        <v>551</v>
       </c>
       <c r="I11" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="J11" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K11" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L11" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M11" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N11" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O11" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P11" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q11" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R11" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S11" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -7448,52 +7893,55 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>534</v>
+        <v>555</v>
       </c>
       <c r="E12" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="F12" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="G12" t="s">
-        <v>524</v>
+        <v>545</v>
       </c>
       <c r="H12" t="s">
+        <v>553</v>
+      </c>
+      <c r="I12" t="s">
+        <v>535</v>
+      </c>
+      <c r="J12" t="s">
+        <v>536</v>
+      </c>
+      <c r="K12" t="s">
+        <v>537</v>
+      </c>
+      <c r="L12" t="s">
+        <v>531</v>
+      </c>
+      <c r="M12" t="s">
+        <v>538</v>
+      </c>
+      <c r="N12" t="s">
+        <v>539</v>
+      </c>
+      <c r="O12" t="s">
         <v>532</v>
       </c>
-      <c r="I12" t="s">
-        <v>515</v>
-      </c>
-      <c r="J12" t="s">
-        <v>516</v>
-      </c>
-      <c r="K12" t="s">
-        <v>511</v>
-      </c>
-      <c r="L12" t="s">
-        <v>517</v>
-      </c>
-      <c r="M12" t="s">
-        <v>518</v>
-      </c>
-      <c r="N12" t="s">
-        <v>512</v>
-      </c>
-      <c r="O12" t="s">
-        <v>519</v>
-      </c>
       <c r="P12" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q12" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -7501,52 +7949,55 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" t="s">
+        <v>531</v>
+      </c>
+      <c r="F13" t="s">
+        <v>543</v>
+      </c>
+      <c r="G13" t="s">
+        <v>547</v>
+      </c>
+      <c r="H13" t="s">
+        <v>551</v>
+      </c>
+      <c r="I13" t="s">
         <v>535</v>
       </c>
-      <c r="E13" t="s">
-        <v>511</v>
-      </c>
-      <c r="F13" t="s">
-        <v>522</v>
-      </c>
-      <c r="G13" t="s">
-        <v>526</v>
-      </c>
-      <c r="H13" t="s">
-        <v>530</v>
-      </c>
-      <c r="I13" t="s">
-        <v>515</v>
-      </c>
       <c r="J13" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
       <c r="K13" t="s">
-        <v>511</v>
+        <v>537</v>
       </c>
       <c r="L13" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M13" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N13" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O13" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P13" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q13" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R13" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -7554,52 +8005,55 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
+        <v>557</v>
+      </c>
+      <c r="E14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" t="s">
+        <v>547</v>
+      </c>
+      <c r="H14" t="s">
+        <v>553</v>
+      </c>
+      <c r="I14" t="s">
+        <v>535</v>
+      </c>
+      <c r="J14" t="s">
         <v>536</v>
       </c>
-      <c r="E14" t="s">
-        <v>511</v>
-      </c>
-      <c r="F14" t="s">
-        <v>512</v>
-      </c>
-      <c r="G14" t="s">
-        <v>526</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="K14" t="s">
+        <v>537</v>
+      </c>
+      <c r="L14" t="s">
+        <v>531</v>
+      </c>
+      <c r="M14" t="s">
+        <v>538</v>
+      </c>
+      <c r="N14" t="s">
+        <v>539</v>
+      </c>
+      <c r="O14" t="s">
         <v>532</v>
       </c>
-      <c r="I14" t="s">
-        <v>515</v>
-      </c>
-      <c r="J14" t="s">
-        <v>516</v>
-      </c>
-      <c r="K14" t="s">
-        <v>511</v>
-      </c>
-      <c r="L14" t="s">
-        <v>517</v>
-      </c>
-      <c r="M14" t="s">
-        <v>518</v>
-      </c>
-      <c r="N14" t="s">
-        <v>512</v>
-      </c>
-      <c r="O14" t="s">
-        <v>519</v>
-      </c>
       <c r="P14" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q14" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R14" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -7607,102 +8061,108 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
+        <v>558</v>
+      </c>
+      <c r="E15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" t="s">
+        <v>532</v>
+      </c>
+      <c r="G15" t="s">
+        <v>549</v>
+      </c>
+      <c r="H15" t="s">
+        <v>551</v>
+      </c>
+      <c r="I15" t="s">
+        <v>535</v>
+      </c>
+      <c r="J15" t="s">
+        <v>536</v>
+      </c>
+      <c r="K15" t="s">
         <v>537</v>
       </c>
-      <c r="E15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F15" t="s">
-        <v>512</v>
-      </c>
-      <c r="G15" t="s">
-        <v>528</v>
-      </c>
-      <c r="H15" t="s">
-        <v>530</v>
-      </c>
-      <c r="I15" t="s">
-        <v>515</v>
-      </c>
-      <c r="J15" t="s">
-        <v>516</v>
-      </c>
-      <c r="K15" t="s">
-        <v>511</v>
-      </c>
       <c r="L15" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="M15" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="N15" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="O15" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="P15" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q15" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R15" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>559</v>
+      </c>
+      <c r="D16" t="s">
+        <v>560</v>
+      </c>
+      <c r="E16" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I16" t="s">
+        <v>535</v>
+      </c>
+      <c r="J16" t="s">
+        <v>536</v>
+      </c>
+      <c r="K16" t="s">
+        <v>537</v>
+      </c>
+      <c r="L16" t="s">
+        <v>531</v>
+      </c>
+      <c r="M16" t="s">
         <v>538</v>
       </c>
-      <c r="D16" t="s">
+      <c r="N16" t="s">
         <v>539</v>
       </c>
-      <c r="E16" t="s">
-        <v>511</v>
-      </c>
-      <c r="F16" t="s">
-        <v>521</v>
-      </c>
-      <c r="G16" t="s">
-        <v>528</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="O16" t="s">
         <v>532</v>
       </c>
-      <c r="I16" t="s">
-        <v>515</v>
-      </c>
-      <c r="J16" t="s">
-        <v>516</v>
-      </c>
-      <c r="K16" t="s">
-        <v>511</v>
-      </c>
-      <c r="L16" t="s">
-        <v>517</v>
-      </c>
-      <c r="M16" t="s">
-        <v>518</v>
-      </c>
-      <c r="N16" t="s">
-        <v>512</v>
-      </c>
-      <c r="O16" t="s">
-        <v>519</v>
-      </c>
       <c r="P16" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="Q16" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="R16" t="s">
-        <v>522</v>
+        <v>542</v>
+      </c>
+      <c r="S16" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7730,10 +8190,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>540</v>
+        <v>561</v>
       </c>
       <c r="D1" t="s">
-        <v>541</v>
+        <v>562</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7747,7 +8207,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7764,12 +8224,12 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>543</v>
+        <v>564</v>
       </c>
       <c r="D3" t="s">
-        <v>544</v>
-      </c>
-      <c r="E3" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7866,61 +8326,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="B1" s="4" t="s">
+      <c r="A1" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>548</v>
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>549</v>
+        <v>570</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C3" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>551</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="4"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="4"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
@@ -7933,7 +8393,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="4"/>
+      <c r="C7" s="5"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
@@ -7946,7 +8406,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
@@ -7958,14 +8418,14 @@
     <row r="11" spans="1:5">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="4"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="C12" s="4"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
@@ -7978,13 +8438,285 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <cols>
+    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="F1" t="s">
+        <v>576</v>
+      </c>
+      <c r="G1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>579</v>
+      </c>
+      <c r="E4" t="s">
+        <v>580</v>
+      </c>
+      <c r="F4" t="s">
+        <v>581</v>
+      </c>
+      <c r="G4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5">
+        <v>50</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E5" t="s">
+        <v>584</v>
+      </c>
+      <c r="F5" t="s">
+        <v>585</v>
+      </c>
+      <c r="G5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" t="s">
+        <v>588</v>
+      </c>
+      <c r="F6" t="s">
+        <v>589</v>
+      </c>
+      <c r="G6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="E7" t="s">
+        <v>592</v>
+      </c>
+      <c r="F7" t="s">
+        <v>593</v>
+      </c>
+      <c r="G7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8">
+        <v>200</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="E8" t="s">
+        <v>595</v>
+      </c>
+      <c r="F8" t="s">
+        <v>596</v>
+      </c>
+      <c r="G8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9">
+        <v>300</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="E9" t="s">
+        <v>598</v>
+      </c>
+      <c r="F9" t="s">
+        <v>599</v>
+      </c>
+      <c r="G9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10">
+        <v>450</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="E10" t="s">
+        <v>602</v>
+      </c>
+      <c r="F10" t="s">
+        <v>603</v>
+      </c>
+      <c r="G10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E11" t="s">
+        <v>606</v>
+      </c>
+      <c r="F11" t="s">
+        <v>607</v>
+      </c>
+      <c r="G11" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12">
+        <v>2500</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="E12" t="s">
+        <v>610</v>
+      </c>
+      <c r="F12" t="s">
+        <v>611</v>
+      </c>
+      <c r="G12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13">
+        <v>12500</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E13" t="s">
+        <v>614</v>
+      </c>
+      <c r="F13" t="s">
+        <v>615</v>
+      </c>
+      <c r="G13" t="s">
+        <v>616</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="28.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="39.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -7994,17 +8726,17 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>552</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>553</v>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>554</v>
+        <v>617</v>
       </c>
       <c r="F1" t="s">
-        <v>555</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8014,11 +8746,11 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -8032,7 +8764,8 @@
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8042,169 +8775,1077 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>556</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>557</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>558</v>
+        <v>619</v>
       </c>
       <c r="F4" t="s">
-        <v>559</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>560</v>
+      <c r="C5" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>561</v>
+        <v>621</v>
       </c>
       <c r="F5" t="s">
-        <v>562</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6">
-        <v>100</v>
-      </c>
-      <c r="D6" t="s">
-        <v>563</v>
+      <c r="C6" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="F6" t="s">
-        <v>565</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7">
-        <v>150</v>
-      </c>
-      <c r="D7" t="s">
-        <v>566</v>
+      <c r="C7" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>567</v>
+        <v>625</v>
       </c>
       <c r="F7" t="s">
-        <v>568</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>569</v>
+      <c r="C8" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>570</v>
+        <v>627</v>
       </c>
       <c r="F8" t="s">
-        <v>571</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9">
-        <v>300</v>
-      </c>
-      <c r="D9" t="s">
-        <v>572</v>
+      <c r="C9" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="F9" t="s">
-        <v>574</v>
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" t="s">
+        <v>631</v>
+      </c>
+      <c r="F10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>638</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>639</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N30"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
+    <col min="9" max="9" width="17.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="12" width="9.58333333333333" customWidth="1"/>
+    <col min="13" max="13" width="21.0833333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D1"/>
+      <c r="E1" t="s">
+        <v>644</v>
+      </c>
+      <c r="F1"/>
+      <c r="G1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I1" t="s">
+        <v>647</v>
+      </c>
+      <c r="J1" t="s">
+        <v>648</v>
+      </c>
+      <c r="K1" t="s">
+        <v>649</v>
+      </c>
+      <c r="L1" t="s">
+        <v>650</v>
+      </c>
+      <c r="M1" t="s">
+        <v>651</v>
+      </c>
+      <c r="N1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E2" t="s">
+        <v>653</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="69.6" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E4" t="s">
+        <v>658</v>
+      </c>
+      <c r="F4" t="s">
+        <v>657</v>
+      </c>
+      <c r="G4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H4" t="s">
+        <v>660</v>
+      </c>
+      <c r="I4" t="s">
+        <v>661</v>
+      </c>
+      <c r="J4" t="s">
+        <v>662</v>
+      </c>
+      <c r="K4" t="s">
+        <v>663</v>
+      </c>
+      <c r="L4" t="s">
+        <v>664</v>
+      </c>
+      <c r="M4" t="s">
+        <v>520</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="G5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>430</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>665</v>
+      </c>
+      <c r="L5" t="s">
+        <v>665</v>
+      </c>
+      <c r="M5" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="G6" t="s">
+        <v>503</v>
+      </c>
+      <c r="H6" t="s">
+        <v>506</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>665</v>
+      </c>
+      <c r="L6" t="s">
+        <v>665</v>
+      </c>
+      <c r="M6" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" t="s">
+        <v>505</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>665</v>
+      </c>
+      <c r="L7" t="s">
+        <v>665</v>
+      </c>
+      <c r="M7" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="D10" t="s">
-        <v>575</v>
-      </c>
-      <c r="E10" t="s">
-        <v>576</v>
-      </c>
-      <c r="F10" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D8" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="G8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" t="s">
+        <v>510</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>665</v>
+      </c>
+      <c r="L8" t="s">
+        <v>665</v>
+      </c>
+      <c r="M8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H9" t="s">
+        <v>507</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>665</v>
+      </c>
+      <c r="L9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M9" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="G10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+      <c r="I10"/>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>665</v>
+      </c>
+      <c r="L10" t="s">
+        <v>665</v>
+      </c>
+      <c r="M10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11">
-        <v>1000</v>
-      </c>
-      <c r="D11" t="s">
-        <v>578</v>
-      </c>
-      <c r="E11" t="s">
-        <v>579</v>
-      </c>
-      <c r="F11" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="C11" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" t="s">
+        <v>504</v>
+      </c>
+      <c r="H11" t="s">
+        <v>505</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>665</v>
+      </c>
+      <c r="L11" t="s">
+        <v>665</v>
+      </c>
+      <c r="M11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12">
-        <v>2500</v>
-      </c>
-      <c r="D12" t="s">
-        <v>581</v>
-      </c>
-      <c r="E12" t="s">
-        <v>582</v>
-      </c>
-      <c r="F12" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="C12" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" t="s">
+        <v>504</v>
+      </c>
+      <c r="H12" t="s">
+        <v>509</v>
+      </c>
+      <c r="I12"/>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>667</v>
+      </c>
+      <c r="L12" t="s">
+        <v>667</v>
+      </c>
+      <c r="M12" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="B13">
-        <v>1009</v>
-      </c>
-      <c r="C13">
-        <v>12500</v>
-      </c>
-      <c r="D13" t="s">
-        <v>584</v>
-      </c>
-      <c r="E13" t="s">
-        <v>585</v>
+        <v>2001</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>429</v>
       </c>
       <c r="F13" t="s">
-        <v>586</v>
+        <v>430</v>
+      </c>
+      <c r="N13" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="N14" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>437</v>
+      </c>
+      <c r="N15" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16">
+        <v>2004</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="F16" t="s">
+        <v>679</v>
+      </c>
+      <c r="N16" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17">
+        <v>2005</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>682</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="N17" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18">
+        <v>2006</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="N18" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <v>2007</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>687</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" t="s">
+        <v>437</v>
+      </c>
+      <c r="N19" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20">
+        <v>2008</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="E20" t="s">
+        <v>678</v>
+      </c>
+      <c r="F20" t="s">
+        <v>679</v>
+      </c>
+      <c r="N20" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>694</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>695</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>696</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23">
+        <v>3003</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>697</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>698</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F23" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25">
+        <v>3005</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>702</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F25" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>705</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>706</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="F27" t="s">
+        <v>459</v>
+      </c>
+      <c r="M27" t="s">
+        <v>707</v>
+      </c>
+      <c r="N27" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28">
+        <v>3008</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F28" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29">
+        <v>3009</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30">
+        <v>3010</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="F30" t="s">
+        <v>467</v>
+      </c>
+      <c r="M30" t="s">
+        <v>707</v>
+      </c>
+      <c r="N30" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main - 副本.xlsx
+++ b/luban-excels/bak/xlsx/Main - 副本.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="786" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -16,6 +16,10 @@
     <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
     <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
+    <sheet name="DesktopActivityState" sheetId="11" r:id="rId11"/>
+    <sheet name="BlindBoxRarityRate" sheetId="12" r:id="rId12"/>
+    <sheet name="BlindBoxRevealPath" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="795">
   <si>
     <t>##var</t>
   </si>
@@ -1730,15 +1734,75 @@
     <t>Cooldown</t>
   </si>
   <si>
+    <t>RewardGroupId</t>
+  </si>
+  <si>
+    <t>DisplayMode</t>
+  </si>
+  <si>
+    <t>CostChips</t>
+  </si>
+  <si>
+    <t>MaxRevealClickCount</t>
+  </si>
+  <si>
+    <t>AutoCollectSeconds</t>
+  </si>
+  <si>
+    <t>FixedRarity</t>
+  </si>
+  <si>
+    <t>UseRarityRate</t>
+  </si>
+  <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
     <t>list,int</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>阶梯价格</t>
   </si>
   <si>
     <t>多少秒之后重置阶梯价格</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>展示方式：RevealUpgrade=普通盲盒升级表演 / DirectReward=活动直接展示</t>
+  </si>
+  <si>
+    <t>基础筹码价格</t>
+  </si>
+  <si>
+    <t>普通盲盒点击次数，默认3</t>
+  </si>
+  <si>
+    <t>奖励展示后自动收起时间(秒)</t>
+  </si>
+  <si>
+    <t>活动盲盒可固定品质，普通盲盒为空</t>
+  </si>
+  <si>
+    <t>是否先抽品质：普通盲盒true，固定品质活动盲盒false</t>
+  </si>
+  <si>
+    <t>是否启用，方便临时关闭</t>
+  </si>
+  <si>
+    <t>经典盲盒</t>
+  </si>
+  <si>
+    <t>RevealUpgrade</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
     <t>##column#var</t>
   </si>
   <si>
@@ -1988,6 +2052,9 @@
     <t>WearGlasses</t>
   </si>
   <si>
+    <t>ShowEquippedEyewearByDefault</t>
+  </si>
+  <si>
     <t>LeftPawAnimation</t>
   </si>
   <si>
@@ -2184,6 +2251,183 @@
   </si>
   <si>
     <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>CanUnequip</t>
+  </si>
+  <si>
+    <t>可脱光吗</t>
+  </si>
+  <si>
+    <t>StateName</t>
+  </si>
+  <si>
+    <t>MinInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MaxInputEventsPerMinute</t>
+  </si>
+  <si>
+    <t>MinDurationSeconds</t>
+  </si>
+  <si>
+    <t>CooldownSeconds</t>
+  </si>
+  <si>
+    <t>EnableTongueFeedback</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>行 ID</t>
+  </si>
+  <si>
+    <t>状态名，给人看的</t>
+  </si>
+  <si>
+    <t>最近一段时间估算输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限，0表示无上限</t>
+  </si>
+  <si>
+    <t>连续满足多久后才切换到该状态，防抖动</t>
+  </si>
+  <si>
+    <t>切换到该状态后至少保持多久</t>
+  </si>
+  <si>
+    <t>要播放的狗狗表现</t>
+  </si>
+  <si>
+    <t>该状态下是否启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>多条规则命中时用，数字越大优先级越高</t>
+  </si>
+  <si>
+    <t>状态名</t>
+  </si>
+  <si>
+    <t>输入频率下限</t>
+  </si>
+  <si>
+    <t>输入频率上限</t>
+  </si>
+  <si>
+    <t>切换状态阈值</t>
+  </si>
+  <si>
+    <t>状态最小持续时间</t>
+  </si>
+  <si>
+    <t>狗表现触发</t>
+  </si>
+  <si>
+    <t>启用吐舌反馈</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>Idle</t>
+  </si>
+  <si>
+    <t>挂机空闲，测试阶段为了快速测试，先调成10秒进入，后续记得改长一些</t>
+  </si>
+  <si>
+    <t>Casual</t>
+  </si>
+  <si>
+    <t>Focused</t>
+  </si>
+  <si>
+    <t>HighEnergy</t>
+  </si>
+  <si>
+    <t>Rarity</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>对应 BlindBox.Id</t>
+  </si>
+  <si>
+    <t>品质权重</t>
+  </si>
+  <si>
+    <t>是否启用</t>
+  </si>
+  <si>
+    <t>盲盒Id</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>FinalRarity</t>
+  </si>
+  <si>
+    <t>StartRarity</t>
+  </si>
+  <si>
+    <t>Step1Upgrade</t>
+  </si>
+  <si>
+    <t>Step2Upgrade</t>
+  </si>
+  <si>
+    <t>Step3Upgrade</t>
+  </si>
+  <si>
+    <t>CanEndEarly</t>
+  </si>
+  <si>
+    <t>对应 BlindBox.Id，0表示通用</t>
+  </si>
+  <si>
+    <t>最终奖励品质</t>
+  </si>
+  <si>
+    <t>初始盲盒品质</t>
+  </si>
+  <si>
+    <t>第一次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>第二次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>第三次点击升级 0/1/2</t>
+  </si>
+  <si>
+    <t>演出路径权重</t>
+  </si>
+  <si>
+    <t>达到最高品质后是否提前结束</t>
+  </si>
+  <si>
+    <t>最终品质</t>
+  </si>
+  <si>
+    <t>初始品质</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>Step3</t>
+  </si>
+  <si>
+    <t>可提前结束</t>
   </si>
 </sst>
 </file>
@@ -2804,20 +3048,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3366,16 +3607,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="2"/>
       <c r="E1" t="s">
         <v>3</v>
       </c>
@@ -3411,16 +3652,16 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="2"/>
       <c r="E2" t="s">
         <v>17</v>
       </c>
@@ -3455,51 +3696,51 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="3" customFormat="1" ht="121.8" spans="1:16">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" ht="121.8" spans="1:16">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E4" t="s">
@@ -6932,6 +7173,895 @@
       </c>
       <c r="N98" t="s">
         <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="4.5" customWidth="1"/>
+    <col min="3" max="3" width="10.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="22.9166666666667" customWidth="1"/>
+    <col min="5" max="5" width="23.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="9" width="21.0833333333333" customWidth="1"/>
+    <col min="10" max="10" width="7.25" customWidth="1"/>
+    <col min="11" max="11" width="59.3333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>738</v>
+      </c>
+      <c r="D1" t="s">
+        <v>739</v>
+      </c>
+      <c r="E1" t="s">
+        <v>740</v>
+      </c>
+      <c r="F1" t="s">
+        <v>741</v>
+      </c>
+      <c r="G1" t="s">
+        <v>742</v>
+      </c>
+      <c r="H1" t="s">
+        <v>663</v>
+      </c>
+      <c r="I1" t="s">
+        <v>743</v>
+      </c>
+      <c r="J1" t="s">
+        <v>744</v>
+      </c>
+      <c r="K1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G2" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2" t="s">
+        <v>674</v>
+      </c>
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="87" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>754</v>
+      </c>
+      <c r="D4" t="s">
+        <v>755</v>
+      </c>
+      <c r="E4" t="s">
+        <v>756</v>
+      </c>
+      <c r="F4" t="s">
+        <v>757</v>
+      </c>
+      <c r="G4" t="s">
+        <v>758</v>
+      </c>
+      <c r="H4" t="s">
+        <v>759</v>
+      </c>
+      <c r="I4" t="s">
+        <v>760</v>
+      </c>
+      <c r="J4" t="s">
+        <v>761</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>762</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>443</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>764</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>80</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="K6" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>765</v>
+      </c>
+      <c r="D7">
+        <v>81</v>
+      </c>
+      <c r="E7">
+        <v>180</v>
+      </c>
+      <c r="F7">
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>458</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>766</v>
+      </c>
+      <c r="D8">
+        <v>181</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>466</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>4</v>
+      </c>
+      <c r="K8" t="s">
+        <v>575</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
+    <col min="3" max="3" width="14.5" customWidth="1"/>
+    <col min="4" max="4" width="9.58333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.83333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>767</v>
+      </c>
+      <c r="E1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>770</v>
+      </c>
+      <c r="F3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>773</v>
+      </c>
+      <c r="F4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E5">
+        <v>8000</v>
+      </c>
+      <c r="F5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>439</v>
+      </c>
+      <c r="E6">
+        <v>1500</v>
+      </c>
+      <c r="F6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>1001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7">
+        <v>450</v>
+      </c>
+      <c r="F7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>1001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>426</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>585</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4" outlineLevelRow="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="3.25" customWidth="1"/>
+    <col min="3" max="3" width="24.75" customWidth="1"/>
+    <col min="4" max="5" width="11.4166666666667" customWidth="1"/>
+    <col min="6" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="11.4166666666667" customWidth="1"/>
+    <col min="10" max="10" width="24.25" customWidth="1"/>
+    <col min="11" max="11" width="8.83333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E1" t="s">
+        <v>776</v>
+      </c>
+      <c r="F1" t="s">
+        <v>777</v>
+      </c>
+      <c r="G1" t="s">
+        <v>778</v>
+      </c>
+      <c r="H1" t="s">
+        <v>779</v>
+      </c>
+      <c r="I1" t="s">
+        <v>768</v>
+      </c>
+      <c r="J1" t="s">
+        <v>780</v>
+      </c>
+      <c r="K1" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E3" t="s">
+        <v>783</v>
+      </c>
+      <c r="F3" t="s">
+        <v>784</v>
+      </c>
+      <c r="G3" t="s">
+        <v>785</v>
+      </c>
+      <c r="H3" t="s">
+        <v>786</v>
+      </c>
+      <c r="I3" t="s">
+        <v>787</v>
+      </c>
+      <c r="J3" t="s">
+        <v>788</v>
+      </c>
+      <c r="K3" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D4" t="s">
+        <v>789</v>
+      </c>
+      <c r="E4" t="s">
+        <v>790</v>
+      </c>
+      <c r="F4" t="s">
+        <v>791</v>
+      </c>
+      <c r="G4" t="s">
+        <v>792</v>
+      </c>
+      <c r="H4" t="s">
+        <v>793</v>
+      </c>
+      <c r="I4" t="s">
+        <v>773</v>
+      </c>
+      <c r="J4" t="s">
+        <v>794</v>
+      </c>
+      <c r="K4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>100</v>
+      </c>
+      <c r="J5" t="s">
+        <v>585</v>
+      </c>
+      <c r="K5" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>426</v>
+      </c>
+      <c r="E6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>80</v>
+      </c>
+      <c r="J6" t="s">
+        <v>585</v>
+      </c>
+      <c r="K6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>432</v>
+      </c>
+      <c r="E7" t="s">
+        <v>446</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7" t="s">
+        <v>585</v>
+      </c>
+      <c r="K7" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" t="s">
+        <v>446</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8" t="s">
+        <v>585</v>
+      </c>
+      <c r="K8" t="s">
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -6951,292 +8081,292 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>4</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>8</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="4">
         <v>16</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="O6" s="5" t="s">
+      <c r="O6" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="P6" s="5" t="s">
+      <c r="P6" s="4" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>462</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="4">
         <v>32</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="O7" s="5" t="s">
+      <c r="O7" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="P7" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="4">
         <v>64</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="O8" s="5" t="s">
+      <c r="O8" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="4">
         <v>128</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="O9" s="5" t="s">
+      <c r="O9" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="P9" s="5" t="s">
+      <c r="P9" s="4" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="4">
         <v>256</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="4">
         <v>512</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>487</v>
       </c>
     </row>
@@ -7247,30 +8377,30 @@
       <c r="C12" t="s">
         <v>488</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="4">
         <v>1024</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="J13" s="5">
+      <c r="J13" s="4">
         <v>2048</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>494</v>
       </c>
     </row>
@@ -7305,26 +8435,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>499</v>
       </c>
       <c r="I1" t="s">
@@ -7362,80 +8492,80 @@
       </c>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="34.8" spans="1:19">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:19">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B4" t="s">
@@ -8174,19 +9304,31 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultColWidth="8.58333333333333" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="20.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="40.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="7.91666666666667" customWidth="1"/>
+    <col min="6" max="6" width="14.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="64.8333333333333" customWidth="1"/>
+    <col min="8" max="8" width="11.4166666666667" customWidth="1"/>
+    <col min="9" max="9" width="21.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="23.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="29.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="44.4166666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.5833333333333" customWidth="1"/>
+    <col min="14" max="14" width="8.16666666666667" customWidth="1"/>
+    <col min="15" max="16384" width="8.58333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -8196,18 +9338,45 @@
         <v>562</v>
       </c>
       <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G1" t="s">
+        <v>564</v>
+      </c>
+      <c r="H1" t="s">
+        <v>565</v>
+      </c>
+      <c r="I1" t="s">
+        <v>566</v>
+      </c>
+      <c r="J1" t="s">
+        <v>567</v>
+      </c>
+      <c r="K1" t="s">
+        <v>568</v>
+      </c>
+      <c r="L1" t="s">
+        <v>569</v>
+      </c>
+      <c r="M1" t="s">
+        <v>570</v>
+      </c>
+      <c r="N1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:14">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -8215,25 +9384,79 @@
       <c r="E2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="D3" t="s">
-        <v>565</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H3" t="s">
+        <v>577</v>
+      </c>
+      <c r="I3" t="s">
+        <v>578</v>
+      </c>
+      <c r="J3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K3" t="s">
+        <v>580</v>
+      </c>
+      <c r="L3" t="s">
+        <v>581</v>
+      </c>
+      <c r="M3" t="s">
+        <v>582</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:14">
       <c r="B4">
         <v>1001</v>
       </c>
@@ -8243,63 +9466,87 @@
       <c r="D4">
         <v>300</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="E4" t="s">
+        <v>583</v>
+      </c>
+      <c r="F4">
+        <v>1001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>584</v>
+      </c>
+      <c r="H4">
+        <v>8000</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>585</v>
+      </c>
+      <c r="M4" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="C5">
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:14">
       <c r="C6">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:14">
       <c r="C7">
         <v>15000</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:14">
       <c r="C8">
         <v>15000</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:14">
       <c r="C9">
         <v>20000</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:14">
       <c r="C10">
         <v>20000</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:14">
       <c r="C11">
         <v>30000</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:14">
       <c r="C12">
         <v>30000</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:14">
       <c r="C13">
         <v>50000</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:14">
       <c r="C14">
         <v>50000</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:14">
       <c r="C15">
         <v>80000</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:14">
       <c r="C16">
         <v>80000</v>
       </c>
@@ -8326,108 +9573,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6"/>
-      <c r="B2" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>569</v>
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>572</v>
+      <c r="D3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="A10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8449,42 +9696,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="D1" t="s">
-        <v>574</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>575</v>
+        <v>594</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="F1" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="G1" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E2" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
@@ -8495,11 +9742,11 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="E3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
@@ -8509,16 +9756,16 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="F4" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="G4" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8528,17 +9775,17 @@
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>583</v>
+      <c r="D5" s="4" t="s">
+        <v>603</v>
       </c>
       <c r="E5" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="F5" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="G5" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8548,17 +9795,17 @@
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>587</v>
+      <c r="D6" s="4" t="s">
+        <v>607</v>
       </c>
       <c r="E6" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="F6" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="G6" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -8568,17 +9815,17 @@
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>591</v>
+      <c r="D7" s="4" t="s">
+        <v>611</v>
       </c>
       <c r="E7" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="F7" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -8588,17 +9835,17 @@
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>595</v>
+      <c r="D8" s="4" t="s">
+        <v>615</v>
       </c>
       <c r="E8" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="F8" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="G8" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -8608,17 +9855,17 @@
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>598</v>
+      <c r="D9" s="4" t="s">
+        <v>618</v>
       </c>
       <c r="E9" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="F9" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="G9" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -8628,17 +9875,17 @@
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>601</v>
+      <c r="D10" s="4" t="s">
+        <v>621</v>
       </c>
       <c r="E10" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="F10" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="G10" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -8648,17 +9895,17 @@
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>605</v>
+      <c r="D11" s="4" t="s">
+        <v>625</v>
       </c>
       <c r="E11" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="F11" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="G11" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -8668,17 +9915,17 @@
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>609</v>
+      <c r="D12" s="4" t="s">
+        <v>629</v>
       </c>
       <c r="E12" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="F12" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="G12" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -8688,17 +9935,17 @@
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>613</v>
+      <c r="D13" s="4" t="s">
+        <v>633</v>
       </c>
       <c r="E13" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="F13" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="G13" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -8720,33 +9967,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="F1" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
@@ -8760,12 +10007,12 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -8781,112 +10028,112 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="F4" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="F5" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>48</v>
       </c>
       <c r="E6" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="F6" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E7" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="F7" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>366</v>
       </c>
       <c r="E8" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="F8" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>454</v>
       </c>
       <c r="E9" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="F9" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>462</v>
       </c>
       <c r="E10" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="F10" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -8907,54 +10154,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="D1" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="E1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="E3" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -8976,7 +10223,7 @@
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="D5" t="s">
         <v>90</v>
@@ -8990,7 +10237,7 @@
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="D6" t="s">
         <v>132</v>
@@ -9004,7 +10251,7 @@
         <v>1004</v>
       </c>
       <c r="C7" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="D7" t="s">
         <v>153</v>
@@ -9028,7 +10275,7 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="D10" t="s">
         <v>204</v>
@@ -9052,7 +10299,7 @@
         <v>1006</v>
       </c>
       <c r="C13" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="D13" t="s">
         <v>413</v>
@@ -9067,44 +10314,44 @@
       </c>
     </row>
     <row r="23" spans="3:4">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
     </row>
     <row r="24" spans="3:4">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
     </row>
     <row r="25" spans="3:4">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
     </row>
     <row r="26" spans="3:4">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
     </row>
     <row r="27" spans="3:4">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
     </row>
     <row r="28" spans="3:4">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
     </row>
     <row r="29" spans="3:4">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
     </row>
     <row r="30" spans="3:4">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
     </row>
     <row r="31" spans="3:4">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
     </row>
     <row r="32" spans="3:4">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9115,74 +10362,73 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="18.75" customWidth="1"/>
     <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="11.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
     <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.5" customWidth="1"/>
-    <col min="9" max="9" width="17.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="11.5" customWidth="1"/>
-    <col min="11" max="12" width="9.58333333333333" customWidth="1"/>
-    <col min="13" max="13" width="21.0833333333333" customWidth="1"/>
-    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="11" width="29.25" customWidth="1"/>
+    <col min="12" max="14" width="9.58333333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="D1"/>
+      <c r="C1" s="2" t="s">
+        <v>663</v>
+      </c>
       <c r="E1" t="s">
-        <v>644</v>
-      </c>
-      <c r="F1"/>
+        <v>664</v>
+      </c>
       <c r="G1" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="H1" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="I1" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="J1" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="K1" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="L1" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="M1" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="N1" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="O1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>653</v>
+      <c r="C2" s="2" t="s">
+        <v>674</v>
       </c>
       <c r="E2" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="G2" t="s">
         <v>16</v>
@@ -9196,9 +10442,6 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
@@ -9208,21 +10451,24 @@
       <c r="N2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="69.6" spans="1:14">
-      <c r="A3" s="2" t="s">
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:15">
+      <c r="A3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="E3" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="E3" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -9230,50 +10476,50 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="D4" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="E4" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="F4" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="G4" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="H4" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="I4" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="J4" t="s">
-        <v>662</v>
-      </c>
-      <c r="K4" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="L4" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="M4" t="s">
+        <v>685</v>
+      </c>
+      <c r="N4" t="s">
         <v>520</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>430</v>
       </c>
       <c r="G5" t="s">
@@ -9282,28 +10528,27 @@
       <c r="H5" t="s">
         <v>430</v>
       </c>
-      <c r="I5"/>
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
-        <v>665</v>
-      </c>
       <c r="L5" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M5" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>436</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>437</v>
       </c>
       <c r="G6" t="s">
@@ -9312,28 +10557,27 @@
       <c r="H6" t="s">
         <v>506</v>
       </c>
-      <c r="I6"/>
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
-        <v>665</v>
-      </c>
       <c r="L6" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M6" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>444</v>
       </c>
       <c r="G7" t="s">
@@ -9342,28 +10586,27 @@
       <c r="H7" t="s">
         <v>505</v>
       </c>
-      <c r="I7"/>
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
-        <v>665</v>
-      </c>
       <c r="L7" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M7" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N7" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>451</v>
       </c>
       <c r="G8" t="s">
@@ -9372,28 +10615,27 @@
       <c r="H8" t="s">
         <v>510</v>
       </c>
-      <c r="I8"/>
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>665</v>
-      </c>
       <c r="L8" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M8" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>459</v>
       </c>
       <c r="G9" t="s">
@@ -9402,28 +10644,27 @@
       <c r="H9" t="s">
         <v>507</v>
       </c>
-      <c r="I9"/>
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>665</v>
-      </c>
       <c r="L9" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M9" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N9" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>467</v>
       </c>
       <c r="G10" t="s">
@@ -9432,28 +10673,27 @@
       <c r="H10" t="s">
         <v>508</v>
       </c>
-      <c r="I10"/>
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>665</v>
-      </c>
       <c r="L10" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M10" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N10" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>473</v>
       </c>
       <c r="G11" t="s">
@@ -9462,28 +10702,27 @@
       <c r="H11" t="s">
         <v>505</v>
       </c>
-      <c r="I11"/>
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>665</v>
-      </c>
       <c r="L11" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="M11" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+        <v>686</v>
+      </c>
+      <c r="N11" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>479</v>
       </c>
       <c r="G12" t="s">
@@ -9492,360 +10731,359 @@
       <c r="H12" t="s">
         <v>509</v>
       </c>
-      <c r="I12"/>
       <c r="J12" t="b">
         <v>1</v>
       </c>
-      <c r="K12" t="s">
-        <v>667</v>
-      </c>
       <c r="L12" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
       <c r="M12" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+        <v>688</v>
+      </c>
+      <c r="N12" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="B13">
         <v>2001</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>668</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>669</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C13" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F13" t="s">
         <v>430</v>
       </c>
-      <c r="N13" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="B14">
         <v>2002</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="C14" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>429</v>
       </c>
       <c r="F14" t="s">
         <v>430</v>
       </c>
-      <c r="N14" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="B15">
         <v>2003</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>674</v>
-      </c>
-      <c r="E15" s="5" t="s">
+      <c r="C15" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F15" t="s">
         <v>437</v>
       </c>
-      <c r="N15" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="B16">
         <v>2004</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>677</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>678</v>
+      <c r="C16" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>699</v>
       </c>
       <c r="F16" t="s">
-        <v>679</v>
-      </c>
-      <c r="N16" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
+        <v>700</v>
+      </c>
+      <c r="O16" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15">
       <c r="B17">
         <v>2005</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="E17" s="5" t="s">
+      <c r="C17" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>472</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="N17" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+      <c r="O17" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15">
       <c r="B18">
         <v>2006</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>684</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>685</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="C18" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>478</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="N18" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
+      <c r="O18" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15">
       <c r="B19">
         <v>2007</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>687</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>688</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="C19" s="4" t="s">
+        <v>708</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>436</v>
       </c>
       <c r="F19" t="s">
         <v>437</v>
       </c>
-      <c r="N19" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
+      <c r="O19" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15">
       <c r="B20">
         <v>2008</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>690</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>691</v>
+      <c r="C20" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="E20" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
-      </c>
-      <c r="N20" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
+        <v>700</v>
+      </c>
+      <c r="O20" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15">
       <c r="B21">
         <v>3001</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>693</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>694</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="C21" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F21" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:15">
       <c r="B22">
         <v>3002</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>695</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>696</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="C22" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>443</v>
       </c>
       <c r="F22" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="23" spans="2:14">
+    <row r="23" spans="2:15">
       <c r="B23">
         <v>3003</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>697</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>698</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="C23" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F23" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="24" spans="2:14">
+    <row r="24" spans="2:15">
       <c r="B24">
         <v>3004</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>699</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>700</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="C24" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>450</v>
       </c>
       <c r="F24" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="25" spans="2:14">
+    <row r="25" spans="2:15">
       <c r="B25">
         <v>3005</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>702</v>
-      </c>
-      <c r="E25" s="5" t="s">
+      <c r="C25" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F25" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="26" spans="2:14">
+    <row r="26" spans="2:15">
       <c r="B26">
         <v>3006</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>703</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>704</v>
-      </c>
-      <c r="E26" s="5" t="s">
+      <c r="C26" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F26" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="27" spans="2:14">
+    <row r="27" spans="2:15">
       <c r="B27">
         <v>3007</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>705</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="C27" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>458</v>
       </c>
       <c r="F27" t="s">
         <v>459</v>
       </c>
-      <c r="M27" t="s">
-        <v>707</v>
-      </c>
       <c r="N27" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
+        <v>728</v>
+      </c>
+      <c r="O27" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15">
       <c r="B28">
         <v>3008</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="E28" s="5" t="s">
+      <c r="C28" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F28" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="29" spans="2:14">
+    <row r="29" spans="2:15">
       <c r="B29">
         <v>3009</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>711</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>712</v>
-      </c>
-      <c r="E29" s="5" t="s">
+      <c r="C29" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F29" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="30" spans="2:14">
+    <row r="30" spans="2:15">
       <c r="B30">
         <v>3010</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="E30" s="5" t="s">
+      <c r="C30" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>466</v>
       </c>
       <c r="F30" t="s">
         <v>467</v>
       </c>
-      <c r="M30" t="s">
-        <v>707</v>
-      </c>
       <c r="N30" t="s">
-        <v>708</v>
+        <v>728</v>
+      </c>
+      <c r="O30" t="s">
+        <v>729</v>
       </c>
     </row>
   </sheetData>
